--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/204.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/204.xlsx
@@ -426,13 +426,13 @@
         <v>-1.809351707637785</v>
       </c>
       <c r="E2">
-        <v>-21.23551562357045</v>
+        <v>-19.88235324839045</v>
       </c>
       <c r="F2">
-        <v>-5.150651977233371</v>
+        <v>-4.306968889523506</v>
       </c>
       <c r="G2">
-        <v>-11.59016811492813</v>
+        <v>-10.05007253514932</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-1.87349809224772</v>
       </c>
       <c r="E3">
-        <v>-21.80483537581476</v>
+        <v>-19.79062447889108</v>
       </c>
       <c r="F3">
-        <v>-4.279497741344466</v>
+        <v>-4.664479006693328</v>
       </c>
       <c r="G3">
-        <v>-10.94651529845533</v>
+        <v>-10.95617878088446</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-1.933809392084981</v>
       </c>
       <c r="E4">
-        <v>-21.8070996128186</v>
+        <v>-21.02592878954745</v>
       </c>
       <c r="F4">
-        <v>-4.996620372152415</v>
+        <v>-4.454831642555815</v>
       </c>
       <c r="G4">
-        <v>-11.57326115885907</v>
+        <v>-10.3247948461802</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-1.973056936671262</v>
       </c>
       <c r="E5">
-        <v>-22.08712686003091</v>
+        <v>-21.41505150407854</v>
       </c>
       <c r="F5">
-        <v>-4.479870704040236</v>
+        <v>-3.759173667889207</v>
       </c>
       <c r="G5">
-        <v>-11.95484125880655</v>
+        <v>-10.30980800652392</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-1.980717199633822</v>
       </c>
       <c r="E6">
-        <v>-24.65306891615312</v>
+        <v>-21.4718204542387</v>
       </c>
       <c r="F6">
-        <v>-5.112146146881639</v>
+        <v>-4.361380202376392</v>
       </c>
       <c r="G6">
-        <v>-11.31219153763215</v>
+        <v>-9.82600488141483</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-1.94537081236744</v>
       </c>
       <c r="E7">
-        <v>-22.67855915085468</v>
+        <v>-22.73732968652623</v>
       </c>
       <c r="F7">
-        <v>-4.507431315898778</v>
+        <v>-4.075388013294668</v>
       </c>
       <c r="G7">
-        <v>-10.40733667811085</v>
+        <v>-10.54112906553496</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-1.860983307186232</v>
       </c>
       <c r="E8">
-        <v>-22.51334683363284</v>
+        <v>-23.6258434576752</v>
       </c>
       <c r="F8">
-        <v>-4.406127781108218</v>
+        <v>-4.112184921694425</v>
       </c>
       <c r="G8">
-        <v>-10.07298813137216</v>
+        <v>-9.897539149427402</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-1.723590515716075</v>
       </c>
       <c r="E9">
-        <v>-26.21936392050412</v>
+        <v>-23.90372873668188</v>
       </c>
       <c r="F9">
-        <v>-4.92784019833057</v>
+        <v>-4.043528174615596</v>
       </c>
       <c r="G9">
-        <v>-10.12188488898719</v>
+        <v>-9.539675797723264</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-1.532199182051182</v>
       </c>
       <c r="E10">
-        <v>-25.55330690650795</v>
+        <v>-25.40432011165559</v>
       </c>
       <c r="F10">
-        <v>-4.916701141865124</v>
+        <v>-4.146109051941273</v>
       </c>
       <c r="G10">
-        <v>-10.63976014878646</v>
+        <v>-9.490216247366554</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-1.290640303717504</v>
       </c>
       <c r="E11">
-        <v>-25.49575000187046</v>
+        <v>-23.87316606560412</v>
       </c>
       <c r="F11">
-        <v>-4.683741033910625</v>
+        <v>-3.947832687141989</v>
       </c>
       <c r="G11">
-        <v>-9.829825250967149</v>
+        <v>-9.277066772820579</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-1.00704075164843</v>
       </c>
       <c r="E12">
-        <v>-28.45879394372528</v>
+        <v>-25.23001914710036</v>
       </c>
       <c r="F12">
-        <v>-5.066266189910186</v>
+        <v>-4.216430817499728</v>
       </c>
       <c r="G12">
-        <v>-9.084035483516754</v>
+        <v>-8.741725074756113</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-0.6895932858411488</v>
       </c>
       <c r="E13">
-        <v>-26.03592902387542</v>
+        <v>-26.31468376989157</v>
       </c>
       <c r="F13">
-        <v>-4.828846980226417</v>
+        <v>-3.673441783536472</v>
       </c>
       <c r="G13">
-        <v>-10.15021653771228</v>
+        <v>-8.611084326685393</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-0.3515715866387695</v>
       </c>
       <c r="E14">
-        <v>-27.34999255447319</v>
+        <v>-26.04446972585388</v>
       </c>
       <c r="F14">
-        <v>-4.537343662813869</v>
+        <v>-3.634745428682096</v>
       </c>
       <c r="G14">
-        <v>-10.2886469994369</v>
+        <v>-7.912062636068282</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-0.006360621058468975</v>
       </c>
       <c r="E15">
-        <v>-29.30580877906796</v>
+        <v>-27.4035508165619</v>
       </c>
       <c r="F15">
-        <v>-4.611108951665761</v>
+        <v>-3.65550100232664</v>
       </c>
       <c r="G15">
-        <v>-10.74616770350972</v>
+        <v>-7.450774531171774</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>0.3369430915588654</v>
       </c>
       <c r="E16">
-        <v>-27.81452794665402</v>
+        <v>-27.02427300452348</v>
       </c>
       <c r="F16">
-        <v>-4.461475149126267</v>
+        <v>-3.729897507139467</v>
       </c>
       <c r="G16">
-        <v>-9.370685690125628</v>
+        <v>-7.251310851885146</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>0.6680063269559467</v>
       </c>
       <c r="E17">
-        <v>-28.71209413734432</v>
+        <v>-28.81699623773201</v>
       </c>
       <c r="F17">
-        <v>-3.854662891879517</v>
+        <v>-3.22138926631774</v>
       </c>
       <c r="G17">
-        <v>-8.554169427774243</v>
+        <v>-8.127426865580031</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>0.9782042243793481</v>
       </c>
       <c r="E18">
-        <v>-30.86131469409569</v>
+        <v>-30.11215338934775</v>
       </c>
       <c r="F18">
-        <v>-4.175007477155336</v>
+        <v>-3.554604195930855</v>
       </c>
       <c r="G18">
-        <v>-7.913492791741247</v>
+        <v>-7.012564239229526</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>1.261825366107479</v>
       </c>
       <c r="E19">
-        <v>-30.25875141416106</v>
+        <v>-29.75943960583832</v>
       </c>
       <c r="F19">
-        <v>-3.408915078963492</v>
+        <v>-3.100473304898499</v>
       </c>
       <c r="G19">
-        <v>-9.170549970094529</v>
+        <v>-6.62494239367288</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>1.510682481350692</v>
       </c>
       <c r="E20">
-        <v>-31.49691998462728</v>
+        <v>-30.69956892372672</v>
       </c>
       <c r="F20">
-        <v>-3.657292761018896</v>
+        <v>-2.271301557350875</v>
       </c>
       <c r="G20">
-        <v>-8.955116219126456</v>
+        <v>-6.82975922509651</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>1.71581280769754</v>
       </c>
       <c r="E21">
-        <v>-32.81174203462133</v>
+        <v>-31.98963833479485</v>
       </c>
       <c r="F21">
-        <v>-4.12709967678183</v>
+        <v>-2.059717470225617</v>
       </c>
       <c r="G21">
-        <v>-9.627915078527</v>
+        <v>-6.880645620580648</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>1.867923924831695</v>
       </c>
       <c r="E22">
-        <v>-31.32748486539329</v>
+        <v>-31.77500225225329</v>
       </c>
       <c r="F22">
-        <v>-3.273906931287826</v>
+        <v>-2.430864171580324</v>
       </c>
       <c r="G22">
-        <v>-8.689603845785827</v>
+        <v>-6.080960171750918</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>1.955223795868622</v>
       </c>
       <c r="E23">
-        <v>-31.40596105570921</v>
+        <v>-31.77538264406994</v>
       </c>
       <c r="F23">
-        <v>-3.017916552800695</v>
+        <v>-2.007779662437491</v>
       </c>
       <c r="G23">
-        <v>-8.001854562729935</v>
+        <v>-6.70793445979687</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>1.966870227774031</v>
       </c>
       <c r="E24">
-        <v>-32.38143737746448</v>
+        <v>-32.61215180697027</v>
       </c>
       <c r="F24">
-        <v>-3.300737751464502</v>
+        <v>-1.810524674645858</v>
       </c>
       <c r="G24">
-        <v>-7.55758597245082</v>
+        <v>-7.011028146099304</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>1.894254561724996</v>
       </c>
       <c r="E25">
-        <v>-32.98266475756684</v>
+        <v>-32.5804117326505</v>
       </c>
       <c r="F25">
-        <v>-3.034951928439266</v>
+        <v>-2.039731449898273</v>
       </c>
       <c r="G25">
-        <v>-8.829990839924161</v>
+        <v>-7.094755153333011</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>1.729361663780077</v>
       </c>
       <c r="E26">
-        <v>-30.75975687176267</v>
+        <v>-32.44637795897147</v>
       </c>
       <c r="F26">
-        <v>-2.629787491321195</v>
+        <v>-1.872378868612897</v>
       </c>
       <c r="G26">
-        <v>-9.472614076734249</v>
+        <v>-7.161389813947462</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>1.470318044374076</v>
       </c>
       <c r="E27">
-        <v>-33.17498452019859</v>
+        <v>-33.17317086635853</v>
       </c>
       <c r="F27">
-        <v>-2.244729187803872</v>
+        <v>-2.015853759512578</v>
       </c>
       <c r="G27">
-        <v>-9.508914208572357</v>
+        <v>-7.151686604971858</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>1.122755400634834</v>
       </c>
       <c r="E28">
-        <v>-32.49770141913741</v>
+        <v>-32.00263052672285</v>
       </c>
       <c r="F28">
-        <v>-2.414249606582374</v>
+        <v>-1.893700217193554</v>
       </c>
       <c r="G28">
-        <v>-8.904981317479733</v>
+        <v>-7.070343190526426</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>0.6947922244472745</v>
       </c>
       <c r="E29">
-        <v>-31.75615474343337</v>
+        <v>-31.34972193700795</v>
       </c>
       <c r="F29">
-        <v>-2.664924351445741</v>
+        <v>-1.495549566874986</v>
       </c>
       <c r="G29">
-        <v>-9.346128063315314</v>
+        <v>-7.335756247500876</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>0.2026478930224072</v>
       </c>
       <c r="E30">
-        <v>-32.14566917096613</v>
+        <v>-30.94213210547358</v>
       </c>
       <c r="F30">
-        <v>-2.805992835040289</v>
+        <v>-1.558282658656395</v>
       </c>
       <c r="G30">
-        <v>-8.31734624207694</v>
+        <v>-7.495721807958459</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-0.330887157089868</v>
       </c>
       <c r="E31">
-        <v>-31.74791518497641</v>
+        <v>-32.36071508040538</v>
       </c>
       <c r="F31">
-        <v>-2.586201283688093</v>
+        <v>-1.719366983804787</v>
       </c>
       <c r="G31">
-        <v>-9.337838457284979</v>
+        <v>-7.733789758778529</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-0.884455051044445</v>
       </c>
       <c r="E32">
-        <v>-30.36446411139612</v>
+        <v>-30.81831004068184</v>
       </c>
       <c r="F32">
-        <v>-2.877948141117065</v>
+        <v>-1.692766449766089</v>
       </c>
       <c r="G32">
-        <v>-8.809650848130879</v>
+        <v>-7.794094656321893</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-1.431285754744624</v>
       </c>
       <c r="E33">
-        <v>-30.15578750064866</v>
+        <v>-30.30008506066607</v>
       </c>
       <c r="F33">
-        <v>-2.386271497552821</v>
+        <v>-1.977874770829026</v>
       </c>
       <c r="G33">
-        <v>-9.314922861062144</v>
+        <v>-7.651913346501274</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-1.943264092986861</v>
       </c>
       <c r="E34">
-        <v>-31.5077407732686</v>
+        <v>-30.43984961820181</v>
       </c>
       <c r="F34">
-        <v>-2.778442991957983</v>
+        <v>-2.069915501321482</v>
       </c>
       <c r="G34">
-        <v>-10.30055172119612</v>
+        <v>-7.852734349459003</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-2.398891711099028</v>
       </c>
       <c r="E35">
-        <v>-28.93308819739264</v>
+        <v>-29.97276016668065</v>
       </c>
       <c r="F35">
-        <v>-2.044177297749098</v>
+        <v>-1.744493023866502</v>
       </c>
       <c r="G35">
-        <v>-10.32876087973625</v>
+        <v>-7.843299294672081</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-2.776951602338334</v>
       </c>
       <c r="E36">
-        <v>-28.36341975264974</v>
+        <v>-30.0059153891278</v>
       </c>
       <c r="F36">
-        <v>-2.091037213358063</v>
+        <v>-1.773022825586319</v>
       </c>
       <c r="G36">
-        <v>-9.568480854460464</v>
+        <v>-8.412527736876525</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-3.061793737429187</v>
       </c>
       <c r="E37">
-        <v>-29.66001016628891</v>
+        <v>-28.84241456233706</v>
       </c>
       <c r="F37">
-        <v>-2.880274196784126</v>
+        <v>-2.025129817689126</v>
       </c>
       <c r="G37">
-        <v>-9.945350048105556</v>
+        <v>-8.325304793553347</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-3.246848054639651</v>
       </c>
       <c r="E38">
-        <v>-27.81272108552496</v>
+        <v>-27.86176898750204</v>
       </c>
       <c r="F38">
-        <v>-2.440969425527075</v>
+        <v>-1.929633966759594</v>
       </c>
       <c r="G38">
-        <v>-10.49762849714893</v>
+        <v>-8.605807317095795</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-3.330896875520469</v>
       </c>
       <c r="E39">
-        <v>-28.33750782437784</v>
+        <v>-27.69054285679801</v>
       </c>
       <c r="F39">
-        <v>-2.093755915174051</v>
+        <v>-1.849897805668322</v>
       </c>
       <c r="G39">
-        <v>-10.06210967873011</v>
+        <v>-8.171523332163122</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-3.31909295091498</v>
       </c>
       <c r="E40">
-        <v>-26.91286801546078</v>
+        <v>-27.86946739331508</v>
       </c>
       <c r="F40">
-        <v>-3.040871441899672</v>
+        <v>-1.9490467568442</v>
       </c>
       <c r="G40">
-        <v>-9.037760677968821</v>
+        <v>-8.03208646459456</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-3.22344119700092</v>
       </c>
       <c r="E41">
-        <v>-27.13647047653752</v>
+        <v>-26.68033540364092</v>
       </c>
       <c r="F41">
-        <v>-1.678267535114889</v>
+        <v>-1.666701869437003</v>
       </c>
       <c r="G41">
-        <v>-9.303660385137544</v>
+        <v>-8.795776351775794</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-3.061542586121937</v>
       </c>
       <c r="E42">
-        <v>-27.76857299242418</v>
+        <v>-24.68187001084191</v>
       </c>
       <c r="F42">
-        <v>-2.41225406950903</v>
+        <v>-2.245309044985832</v>
       </c>
       <c r="G42">
-        <v>-9.907712455869582</v>
+        <v>-8.190863539203544</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-2.853681985835474</v>
       </c>
       <c r="E43">
-        <v>-25.70376092693879</v>
+        <v>-26.02404177960528</v>
       </c>
       <c r="F43">
-        <v>-2.805660659711766</v>
+        <v>-2.116844171424879</v>
       </c>
       <c r="G43">
-        <v>-9.522457650373516</v>
+        <v>-7.792283787911911</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-2.621137880353348</v>
       </c>
       <c r="E44">
-        <v>-24.63783060111731</v>
+        <v>-25.57799614679777</v>
       </c>
       <c r="F44">
-        <v>-2.289277129991624</v>
+        <v>-1.82384068064586</v>
       </c>
       <c r="G44">
-        <v>-10.78872807696259</v>
+        <v>-8.542205116195317</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-2.387490427910778</v>
       </c>
       <c r="E45">
-        <v>-25.28514426119573</v>
+        <v>-25.02665896483791</v>
       </c>
       <c r="F45">
-        <v>-2.665615209859676</v>
+        <v>-1.981688574351515</v>
       </c>
       <c r="G45">
-        <v>-10.07315034810358</v>
+        <v>-8.309149331321704</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-2.173991211321951</v>
       </c>
       <c r="E46">
-        <v>-22.5355771125365</v>
+        <v>-24.37236692631366</v>
       </c>
       <c r="F46">
-        <v>-2.99404217588461</v>
+        <v>-1.973122427039165</v>
       </c>
       <c r="G46">
-        <v>-10.89896924342032</v>
+        <v>-8.529956097700014</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-1.995677901586077</v>
       </c>
       <c r="E47">
-        <v>-24.51256395311713</v>
+        <v>-23.37218098613554</v>
       </c>
       <c r="F47">
-        <v>-1.930311571295084</v>
+        <v>-1.966015034723145</v>
       </c>
       <c r="G47">
-        <v>-10.67359392419781</v>
+        <v>-8.992343303715559</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-1.866496923488957</v>
       </c>
       <c r="E48">
-        <v>-22.67568356985981</v>
+        <v>-24.38169105429546</v>
       </c>
       <c r="F48">
-        <v>-2.489621099828296</v>
+        <v>-1.872899083341856</v>
       </c>
       <c r="G48">
-        <v>-10.07050191167216</v>
+        <v>-8.564763173499911</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-1.796246854149484</v>
       </c>
       <c r="E49">
-        <v>-23.24084165449108</v>
+        <v>-22.74531791467576</v>
       </c>
       <c r="F49">
-        <v>-2.452058779948352</v>
+        <v>-1.653425625072335</v>
       </c>
       <c r="G49">
-        <v>-9.719766164514079</v>
+        <v>-8.374936492278101</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-1.785152346801892</v>
       </c>
       <c r="E50">
-        <v>-22.05106209303382</v>
+        <v>-22.3000738217676</v>
       </c>
       <c r="F50">
-        <v>-2.723110534553184</v>
+        <v>-1.878754812512245</v>
       </c>
       <c r="G50">
-        <v>-9.790072220131581</v>
+        <v>-8.479708637504956</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-1.83314746385822</v>
       </c>
       <c r="E51">
-        <v>-22.34278186013394</v>
+        <v>-21.27114112858879</v>
       </c>
       <c r="F51">
-        <v>-1.849709766267886</v>
+        <v>-1.984743593333039</v>
       </c>
       <c r="G51">
-        <v>-10.10203816847926</v>
+        <v>-7.795634059997654</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-1.938814565081698</v>
       </c>
       <c r="E52">
-        <v>-20.18462435992844</v>
+        <v>-20.67220515633431</v>
       </c>
       <c r="F52">
-        <v>-2.388734233841344</v>
+        <v>-1.731259026239377</v>
       </c>
       <c r="G52">
-        <v>-12.03314228190139</v>
+        <v>-8.547270250870403</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-2.091181315250466</v>
       </c>
       <c r="E53">
-        <v>-20.68846690649585</v>
+        <v>-20.51174773682052</v>
       </c>
       <c r="F53">
-        <v>-2.788583865703054</v>
+        <v>-1.400974860497366</v>
       </c>
       <c r="G53">
-        <v>-10.20918066431223</v>
+        <v>-8.870028577676107</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-2.282110877474392</v>
       </c>
       <c r="E54">
-        <v>-20.74746386586778</v>
+        <v>-19.9059964111845</v>
       </c>
       <c r="F54">
-        <v>-2.847471676000668</v>
+        <v>-1.965354825903114</v>
       </c>
       <c r="G54">
-        <v>-10.36575291559206</v>
+        <v>-9.889289269943538</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-2.504576776571033</v>
       </c>
       <c r="E55">
-        <v>-19.92673682213963</v>
+        <v>-19.65788132030424</v>
       </c>
       <c r="F55">
-        <v>-1.734484688905878</v>
+        <v>-1.693771259425685</v>
       </c>
       <c r="G55">
-        <v>-10.57435370056708</v>
+        <v>-8.84003503509031</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-2.744071564514972</v>
       </c>
       <c r="E56">
-        <v>-19.82719643497703</v>
+        <v>-19.92728929596856</v>
       </c>
       <c r="F56">
-        <v>-2.136493046219283</v>
+        <v>-1.787342812878514</v>
       </c>
       <c r="G56">
-        <v>-11.54848834658871</v>
+        <v>-9.633162293206745</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-2.989797928366639</v>
       </c>
       <c r="E57">
-        <v>-20.76201838132843</v>
+        <v>-19.04368439064391</v>
       </c>
       <c r="F57">
-        <v>-2.762950036423423</v>
+        <v>-1.206004510002655</v>
       </c>
       <c r="G57">
-        <v>-11.77288374433159</v>
+        <v>-9.401669085827667</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-3.234187709936734</v>
       </c>
       <c r="E58">
-        <v>-17.70780267227719</v>
+        <v>-18.79852639329066</v>
       </c>
       <c r="F58">
-        <v>-1.309028563888829</v>
+        <v>-1.871462694265401</v>
       </c>
       <c r="G58">
-        <v>-12.24343475564697</v>
+        <v>-9.989436583052031</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-3.466587644187039</v>
       </c>
       <c r="E59">
-        <v>-18.10288938707638</v>
+        <v>-20.50936123101848</v>
       </c>
       <c r="F59">
-        <v>-2.20413421486228</v>
+        <v>-1.857366366171962</v>
       </c>
       <c r="G59">
-        <v>-10.5411323760805</v>
+        <v>-10.23941256617686</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-3.680295613510696</v>
       </c>
       <c r="E60">
-        <v>-18.94200203527568</v>
+        <v>-18.3608357950273</v>
       </c>
       <c r="F60">
-        <v>-2.085912932604346</v>
+        <v>-1.552783955836612</v>
       </c>
       <c r="G60">
-        <v>-10.85551502267185</v>
+        <v>-9.88796505172783</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-3.873545019208725</v>
       </c>
       <c r="E61">
-        <v>-19.6230256558672</v>
+        <v>-19.08771021494648</v>
       </c>
       <c r="F61">
-        <v>-1.715934229287586</v>
+        <v>-1.618599402723838</v>
       </c>
       <c r="G61">
-        <v>-11.77088748537141</v>
+        <v>-9.732660739389539</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-4.042331803466072</v>
       </c>
       <c r="E62">
-        <v>-18.09259163718294</v>
+        <v>-18.78625422872987</v>
       </c>
       <c r="F62">
-        <v>-2.687223173561701</v>
+        <v>-1.42541998255398</v>
       </c>
       <c r="G62">
-        <v>-12.8950395025051</v>
+        <v>-10.69513895456739</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-4.18337663361726</v>
       </c>
       <c r="E63">
-        <v>-19.17287722560874</v>
+        <v>-19.43935075011609</v>
       </c>
       <c r="F63">
-        <v>-2.44440632188129</v>
+        <v>-1.670996954420518</v>
       </c>
       <c r="G63">
-        <v>-12.69349680061982</v>
+        <v>-9.448188871745506</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-4.297542775941853</v>
       </c>
       <c r="E64">
-        <v>-18.26104181332026</v>
+        <v>-16.94358645569075</v>
       </c>
       <c r="F64">
-        <v>-1.917804880247617</v>
+        <v>-1.856243099973766</v>
       </c>
       <c r="G64">
-        <v>-11.2026820017386</v>
+        <v>-10.67180622960661</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-4.383321178209322</v>
       </c>
       <c r="E65">
-        <v>-19.42283087693611</v>
+        <v>-17.85159077896873</v>
       </c>
       <c r="F65">
-        <v>-2.089204864663071</v>
+        <v>-2.330891823206063</v>
       </c>
       <c r="G65">
-        <v>-12.55429829233008</v>
+        <v>-10.21631488994936</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-4.437283839697013</v>
       </c>
       <c r="E66">
-        <v>-17.0804686395206</v>
+        <v>-17.87103151788366</v>
       </c>
       <c r="F66">
-        <v>-2.519937690035952</v>
+        <v>-2.045084360055164</v>
       </c>
       <c r="G66">
-        <v>-11.32727107256353</v>
+        <v>-9.674673223723666</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-4.460882224851605</v>
       </c>
       <c r="E67">
-        <v>-18.03925979879461</v>
+        <v>-16.51646078728728</v>
       </c>
       <c r="F67">
-        <v>-2.724034992574708</v>
+        <v>-2.028969300601102</v>
       </c>
       <c r="G67">
-        <v>-11.53922212962429</v>
+        <v>-9.672451847666814</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-4.455749700181305</v>
       </c>
       <c r="E68">
-        <v>-17.37202085308244</v>
+        <v>-17.77452067983219</v>
       </c>
       <c r="F68">
-        <v>-3.418234212244986</v>
+        <v>-1.850222525690219</v>
       </c>
       <c r="G68">
-        <v>-11.70616963062419</v>
+        <v>-9.610005027159541</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-4.420467341781649</v>
       </c>
       <c r="E69">
-        <v>-16.9864756330174</v>
+        <v>-17.16420465239644</v>
       </c>
       <c r="F69">
-        <v>-2.272302225173457</v>
+        <v>-1.807023165634225</v>
       </c>
       <c r="G69">
-        <v>-12.75371562397916</v>
+        <v>-10.49416235596932</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-4.356489333829469</v>
       </c>
       <c r="E70">
-        <v>-18.18375434743135</v>
+        <v>-16.06771165549719</v>
       </c>
       <c r="F70">
-        <v>-2.360078520276301</v>
+        <v>-2.126777124951848</v>
       </c>
       <c r="G70">
-        <v>-12.05559771229427</v>
+        <v>-10.22456145888769</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-4.265884414721956</v>
       </c>
       <c r="E71">
-        <v>-18.74023587586393</v>
+        <v>-16.08315828033735</v>
       </c>
       <c r="F71">
-        <v>-2.85333403211028</v>
+        <v>-2.603015485230117</v>
       </c>
       <c r="G71">
-        <v>-10.82648815938352</v>
+        <v>-9.142416954101801</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-4.1452947257122</v>
       </c>
       <c r="E72">
-        <v>-18.84614782595532</v>
+        <v>-18.01984623072373</v>
       </c>
       <c r="F72">
-        <v>-3.299523364851998</v>
+        <v>-2.429141995749904</v>
       </c>
       <c r="G72">
-        <v>-10.56117772932078</v>
+        <v>-9.476858196115595</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-3.99110095143328</v>
       </c>
       <c r="E73">
-        <v>-17.9900760425973</v>
+        <v>-17.21476053621807</v>
       </c>
       <c r="F73">
-        <v>-3.000061093433351</v>
+        <v>-2.182551102182339</v>
       </c>
       <c r="G73">
-        <v>-11.7380104576209</v>
+        <v>-9.806932828563088</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-3.803869906806078</v>
       </c>
       <c r="E74">
-        <v>-17.09451596589239</v>
+        <v>-16.43628415498148</v>
       </c>
       <c r="F74">
-        <v>-3.220062221738455</v>
+        <v>-2.904244664318935</v>
       </c>
       <c r="G74">
-        <v>-10.94133429468637</v>
+        <v>-8.357294595099326</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-3.580190582680082</v>
       </c>
       <c r="E75">
-        <v>-20.18601007297479</v>
+        <v>-17.87475845199198</v>
       </c>
       <c r="F75">
-        <v>-3.093600340557471</v>
+        <v>-2.255763869976565</v>
       </c>
       <c r="G75">
-        <v>-10.41550379395623</v>
+        <v>-9.106242622994184</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-3.316203026374595</v>
       </c>
       <c r="E76">
-        <v>-17.34146723895268</v>
+        <v>-17.03911461488256</v>
       </c>
       <c r="F76">
-        <v>-3.271351417850189</v>
+        <v>-2.525939211869235</v>
       </c>
       <c r="G76">
-        <v>-10.39159503407162</v>
+        <v>-9.379816174722938</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-3.014953216948169</v>
       </c>
       <c r="E77">
-        <v>-19.13068090480526</v>
+        <v>-17.12436313807695</v>
       </c>
       <c r="F77">
-        <v>-3.974549192617078</v>
+        <v>-2.863378815236627</v>
       </c>
       <c r="G77">
-        <v>-10.15910866303076</v>
+        <v>-9.275759107332567</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-2.678537642657931</v>
       </c>
       <c r="E78">
-        <v>-18.9465622086014</v>
+        <v>-18.11142556058084</v>
       </c>
       <c r="F78">
-        <v>-3.991924198890798</v>
+        <v>-3.213514805786728</v>
       </c>
       <c r="G78">
-        <v>-9.975327037963657</v>
+        <v>-8.710013359035434</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-2.30847835751419</v>
       </c>
       <c r="E79">
-        <v>-19.29139191886348</v>
+        <v>-18.80743843013775</v>
       </c>
       <c r="F79">
-        <v>-3.196478601780753</v>
+        <v>-3.364652923529706</v>
       </c>
       <c r="G79">
-        <v>-9.713684692358438</v>
+        <v>-8.936597027379772</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-1.913199059061582</v>
       </c>
       <c r="E80">
-        <v>-19.56569064645609</v>
+        <v>-18.94770791252535</v>
       </c>
       <c r="F80">
-        <v>-4.194849361554593</v>
+        <v>-2.647308290257807</v>
       </c>
       <c r="G80">
-        <v>-9.798239335976962</v>
+        <v>-8.531915940659262</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-1.502053291679687</v>
       </c>
       <c r="E81">
-        <v>-20.04272462689809</v>
+        <v>-19.54844168896087</v>
       </c>
       <c r="F81">
-        <v>-3.641317695655907</v>
+        <v>-2.976413689185634</v>
       </c>
       <c r="G81">
-        <v>-9.555718701406573</v>
+        <v>-8.021039174130012</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-1.083194954147294</v>
       </c>
       <c r="E82">
-        <v>-20.89935794103306</v>
+        <v>-21.2272239876624</v>
       </c>
       <c r="F82">
-        <v>-4.041058811387851</v>
+        <v>-3.158334767984044</v>
       </c>
       <c r="G82">
-        <v>-8.305957965421847</v>
+        <v>-7.202847775735755</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-0.6683333079895459</v>
       </c>
       <c r="E83">
-        <v>-21.5502219247335</v>
+        <v>-22.1279782240541</v>
       </c>
       <c r="F83">
-        <v>-4.358373228704229</v>
+        <v>-3.245232993639921</v>
       </c>
       <c r="G83">
-        <v>-9.17825692010995</v>
+        <v>-7.148611108165875</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-0.2692398986202852</v>
       </c>
       <c r="E84">
-        <v>-23.29955784847454</v>
+        <v>-22.04819556898697</v>
       </c>
       <c r="F84">
-        <v>-3.571357926652475</v>
+        <v>-3.559197493179378</v>
       </c>
       <c r="G84">
-        <v>-8.967361927076219</v>
+        <v>-7.308179403158746</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>0.1052366345139451</v>
       </c>
       <c r="E85">
-        <v>-23.75081122639087</v>
+        <v>-22.29307280095174</v>
       </c>
       <c r="F85">
-        <v>-4.473753210770561</v>
+        <v>-3.460820580422909</v>
       </c>
       <c r="G85">
-        <v>-8.612832294730129</v>
+        <v>-7.042047957802275</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>0.4459296878153787</v>
       </c>
       <c r="E86">
-        <v>-24.40688295520013</v>
+        <v>-23.70723824948907</v>
       </c>
       <c r="F86">
-        <v>-4.228629355873354</v>
+        <v>-3.337763289267431</v>
       </c>
       <c r="G86">
-        <v>-9.475586946628514</v>
+        <v>-6.69303369432461</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>0.7433319173882444</v>
       </c>
       <c r="E87">
-        <v>-26.37128063803944</v>
+        <v>-24.82670872350323</v>
       </c>
       <c r="F87">
-        <v>-4.249226711343963</v>
+        <v>-3.791349942916148</v>
       </c>
       <c r="G87">
-        <v>-7.818122595845924</v>
+        <v>-6.087203860637983</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>0.9920114955702346</v>
       </c>
       <c r="E88">
-        <v>-25.73658330654638</v>
+        <v>-25.03127800832573</v>
       </c>
       <c r="F88">
-        <v>-4.862959149873701</v>
+        <v>-3.724964579255796</v>
       </c>
       <c r="G88">
-        <v>-8.245437882418431</v>
+        <v>-6.559032742531531</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>1.187447637231462</v>
       </c>
       <c r="E89">
-        <v>-27.60400824698544</v>
+        <v>-26.61611258526414</v>
       </c>
       <c r="F89">
-        <v>-5.045942195682501</v>
+        <v>-4.19672727045674</v>
       </c>
       <c r="G89">
-        <v>-8.298979335425063</v>
+        <v>-6.708450904900996</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>1.323586908532331</v>
       </c>
       <c r="E90">
-        <v>-31.30472475503074</v>
+        <v>-27.72711934135797</v>
       </c>
       <c r="F90">
-        <v>-4.593316448221031</v>
+        <v>-4.303733286448171</v>
       </c>
       <c r="G90">
-        <v>-8.517170770827349</v>
+        <v>-7.266065953353678</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>1.397779609867757</v>
       </c>
       <c r="E91">
-        <v>-29.86418773810975</v>
+        <v>-29.2908919856867</v>
       </c>
       <c r="F91">
-        <v>-5.730197693049573</v>
+        <v>-4.26630184861787</v>
       </c>
       <c r="G91">
-        <v>-7.419923557291306</v>
+        <v>-7.00537042377269</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>1.407459474191643</v>
       </c>
       <c r="E92">
-        <v>-32.1904014372139</v>
+        <v>-31.15848447966403</v>
       </c>
       <c r="F92">
-        <v>-5.364027823050885</v>
+        <v>-4.062869725103562</v>
       </c>
       <c r="G92">
-        <v>-8.486068195485895</v>
+        <v>-6.596763030042604</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>1.349656590182917</v>
       </c>
       <c r="E93">
-        <v>-33.07150209641232</v>
+        <v>-31.15873354573446</v>
       </c>
       <c r="F93">
-        <v>-5.358272326336234</v>
+        <v>-4.432535305542063</v>
       </c>
       <c r="G93">
-        <v>-8.564034853481271</v>
+        <v>-7.837499218887277</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>1.225844375309159</v>
       </c>
       <c r="E94">
-        <v>-35.30397185508369</v>
+        <v>-34.93881608923818</v>
       </c>
       <c r="F94">
-        <v>-5.6599595925988</v>
+        <v>-4.637830427345268</v>
       </c>
       <c r="G94">
-        <v>-9.545121645135366</v>
+        <v>-8.233185553377588</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>1.038317872556956</v>
       </c>
       <c r="E95">
-        <v>-37.82727832842368</v>
+        <v>-35.57614672836669</v>
       </c>
       <c r="F95">
-        <v>-5.520542045238032</v>
+        <v>-5.184800595046378</v>
       </c>
       <c r="G95">
-        <v>-9.119647021882693</v>
+        <v>-8.410594378281591</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>0.7867216477229859</v>
       </c>
       <c r="E96">
-        <v>-39.06601748661486</v>
+        <v>-37.2240312489139</v>
       </c>
       <c r="F96">
-        <v>-5.699751049159677</v>
+        <v>-4.872386799284961</v>
       </c>
       <c r="G96">
-        <v>-9.607118231449297</v>
+        <v>-7.877864700647611</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>0.4832337990620852</v>
       </c>
       <c r="E97">
-        <v>-40.59934746442703</v>
+        <v>-40.59800250764675</v>
       </c>
       <c r="F97">
-        <v>-6.61437469287789</v>
+        <v>-5.391117093857234</v>
       </c>
       <c r="G97">
-        <v>-11.19098584434835</v>
+        <v>-8.932121169810678</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>0.1235075912778729</v>
       </c>
       <c r="E98">
-        <v>-43.02123423389124</v>
+        <v>-42.63128054437973</v>
       </c>
       <c r="F98">
-        <v>-6.398120684519349</v>
+        <v>-5.723257630948919</v>
       </c>
       <c r="G98">
-        <v>-10.05972939648738</v>
+        <v>-9.144300654513646</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-0.2693658062806371</v>
       </c>
       <c r="E99">
-        <v>-44.45777034402644</v>
+        <v>-44.03167716769673</v>
       </c>
       <c r="F99">
-        <v>-7.049323079963618</v>
+        <v>-5.801837391145883</v>
       </c>
       <c r="G99">
-        <v>-10.25767022482594</v>
+        <v>-8.246626368267028</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-0.7106697929920108</v>
       </c>
       <c r="E100">
-        <v>-46.46231974165477</v>
+        <v>-46.27993997946985</v>
       </c>
       <c r="F100">
-        <v>-6.835688369332729</v>
+        <v>-5.804101319257733</v>
       </c>
       <c r="G100">
-        <v>-12.33655047003006</v>
+        <v>-10.01085912323665</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-1.154335749404666</v>
       </c>
       <c r="E101">
-        <v>-51.26337618526883</v>
+        <v>-47.83731615426274</v>
       </c>
       <c r="F101">
-        <v>-7.259409478824614</v>
+        <v>-6.161040691287027</v>
       </c>
       <c r="G101">
-        <v>-10.20493985547643</v>
+        <v>-9.737696079154771</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-1.658582914069498</v>
       </c>
       <c r="E102">
-        <v>-50.5754409812231</v>
+        <v>-51.1612862672399</v>
       </c>
       <c r="F102">
-        <v>-7.175735673284135</v>
+        <v>-6.292254087890468</v>
       </c>
       <c r="G102">
-        <v>-12.60121865425817</v>
+        <v>-10.50283267473667</v>
       </c>
     </row>
   </sheetData>
